--- a/Result/profitability/6213.xlsx
+++ b/Result/profitability/6213.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,13 +669,13 @@
         <v>0.86</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8975</v>
+        <v>1.25125</v>
       </c>
       <c r="N2" t="n">
-        <v>13.4725</v>
+        <v>14.75875</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
@@ -687,7 +687,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0.93</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9275</v>
+        <v>1.2925</v>
       </c>
       <c r="N3" t="n">
-        <v>13.76125</v>
+        <v>14.84625</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
@@ -798,7 +798,7 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -899,13 +899,13 @@
         <v>0.98</v>
       </c>
       <c r="M4" t="n">
-        <v>0.975</v>
+        <v>1.29875</v>
       </c>
       <c r="N4" t="n">
-        <v>13.82625</v>
+        <v>14.79875</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
@@ -917,7 +917,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.93</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7424999999999999</v>
+        <v>1.0375</v>
       </c>
       <c r="N5" t="n">
-        <v>12.59875</v>
+        <v>13.4025</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.53</v>
       </c>
       <c r="M6" t="n">
-        <v>0.66375</v>
+        <v>0.9924999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>12.75875</v>
+        <v>13.795</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1152,7 +1152,7 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1264,13 +1264,13 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6387499999999999</v>
+        <v>0.93125</v>
       </c>
       <c r="N7" t="n">
-        <v>13.19375</v>
+        <v>14.17875</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1279,10 +1279,10 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>1.02</v>
       </c>
       <c r="M8" t="n">
-        <v>0.61875</v>
+        <v>0.95</v>
       </c>
       <c r="N8" t="n">
-        <v>13.15375</v>
+        <v>14.47875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1403,7 +1403,7 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>0.65</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5912499999999999</v>
+        <v>0.5912500000000001</v>
       </c>
       <c r="N9" t="n">
         <v>13.34625</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6213</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>11530</v>
+      </c>
+      <c r="D75" t="n">
+        <v>8991</v>
+      </c>
+      <c r="E75" t="n">
+        <v>2539</v>
+      </c>
+      <c r="F75" t="n">
+        <v>22.02</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1848</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>16.03%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-14</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1834</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1279</v>
+      </c>
+      <c r="L75" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="N75" t="n">
+        <v>14.52625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="X75" t="n">
+        <v>3.045977011494253</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.9281961471103328</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>2.03448275862069</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.4124438742783836</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
